--- a/server-side/modelling/results/taylor svm tables.xlsx
+++ b/server-side/modelling/results/taylor svm tables.xlsx
@@ -17,6 +17,14 @@
     <sheet name="taylor svm 1 0p001 metrics" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="taylor svm 10 0p1 cm" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="taylor svm 10 0p1 metrics" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="taylor svm 10 0p001 cm" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="taylor svm 10 0p001 metrics" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="taylor svm 100 0p1 cm" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="taylor svm 100 0p1 metrics" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="taylor svm 100 0p01 cm" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="taylor svm 100 0p01 metrics" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="taylor svm 1000 0p001 cm" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="taylor svm 1000 0p001 metrics" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -915,6 +923,1954 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>true_negative</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>false_positive</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>false_negative</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>true_positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>afegip_expert1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>7128</v>
+      </c>
+      <c r="C2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4122</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ajeric_expert2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>11357</v>
+      </c>
+      <c r="C3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1324</v>
+      </c>
+      <c r="E3" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ekamis_expert2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>12408</v>
+      </c>
+      <c r="C4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1142</v>
+      </c>
+      <c r="E4" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>iguted_expert1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>11619</v>
+      </c>
+      <c r="C5" t="n">
+        <v>36</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1257</v>
+      </c>
+      <c r="E5" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>inefoh_expert1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>12498</v>
+      </c>
+      <c r="C6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D6" t="n">
+        <v>765</v>
+      </c>
+      <c r="E6" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>otafeh_expert1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>11313</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>543</v>
+      </c>
+      <c r="E7" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>oxused_expert2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>9889</v>
+      </c>
+      <c r="C8" t="n">
+        <v>21</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1828</v>
+      </c>
+      <c r="E8" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pqbqpr_expert2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>14271</v>
+      </c>
+      <c r="C9" t="n">
+        <v>54</v>
+      </c>
+      <c r="D9" t="n">
+        <v>859</v>
+      </c>
+      <c r="E9" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>uhepah_expert1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>11108</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>893</v>
+      </c>
+      <c r="E10" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ukudab_expert2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>12691</v>
+      </c>
+      <c r="C11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1551</v>
+      </c>
+      <c r="E11" t="n">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>acc</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>roc_auc</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>prec</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>rec</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>afegip_expert1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.6688218390804598</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.6037117158506877</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.8541745401698556</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.781680548810102</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.6688218390804598</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ajeric_expert2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.8953096860073604</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.8521371548173298</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.793344652048386</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8911997841839777</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8953096860073604</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ekamis_expert2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.914678023349732</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.8785319737873433</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.707807077920797</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8977417773347691</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.914678023349732</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>iguted_expert1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9015607156452227</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8694520899213385</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.8261449673611836</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.8977148070154384</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9015607156452227</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>inefoh_expert1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.9413919413919414</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9197955575938286</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.78698848635623</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9353140011362132</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9413919413919414</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>otafeh_expert1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.9537829223284684</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9357810072754044</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7731339767172487</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9503987836396851</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9537829223284684</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>oxused_expert2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.8453237410071942</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.7905185829638657</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8711127643902756</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.8555128743987935</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8453237410071942</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pqbqpr_expert2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.9403852432255958</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9207786484723729</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7823548574752763</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9280268100617109</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9403852432255958</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>uhepah_expert1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.9258551976087679</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.8934719988955298</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8639466165911071</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9313723468909418</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9258551976087679</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ukudab_expert2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.8899769182345947</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.8417779110677597</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.7723118266754703</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.8588454263106587</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.8899769182345947</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>true_negative</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>false_positive</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>false_negative</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>true_positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>afegip_expert1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>6688</v>
+      </c>
+      <c r="C2" t="n">
+        <v>467</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2295</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3078</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ajeric_expert2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>11299</v>
+      </c>
+      <c r="C3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1112</v>
+      </c>
+      <c r="E3" t="n">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ekamis_expert2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>12366</v>
+      </c>
+      <c r="C4" t="n">
+        <v>62</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1032</v>
+      </c>
+      <c r="E4" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>iguted_expert1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>11564</v>
+      </c>
+      <c r="C5" t="n">
+        <v>91</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1075</v>
+      </c>
+      <c r="E5" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>inefoh_expert1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>12453</v>
+      </c>
+      <c r="C6" t="n">
+        <v>64</v>
+      </c>
+      <c r="D6" t="n">
+        <v>665</v>
+      </c>
+      <c r="E6" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>otafeh_expert1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>11297</v>
+      </c>
+      <c r="C7" t="n">
+        <v>24</v>
+      </c>
+      <c r="D7" t="n">
+        <v>502</v>
+      </c>
+      <c r="E7" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>oxused_expert2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>9845</v>
+      </c>
+      <c r="C8" t="n">
+        <v>65</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1592</v>
+      </c>
+      <c r="E8" t="n">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pqbqpr_expert2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>14142</v>
+      </c>
+      <c r="C9" t="n">
+        <v>183</v>
+      </c>
+      <c r="D9" t="n">
+        <v>738</v>
+      </c>
+      <c r="E9" t="n">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>uhepah_expert1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>11019</v>
+      </c>
+      <c r="C10" t="n">
+        <v>89</v>
+      </c>
+      <c r="D10" t="n">
+        <v>585</v>
+      </c>
+      <c r="E10" t="n">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ukudab_expert2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>12599</v>
+      </c>
+      <c r="C11" t="n">
+        <v>114</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1366</v>
+      </c>
+      <c r="E11" t="n">
+        <v>218</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>acc</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>roc_auc</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>prec</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>rec</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>afegip_expert1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.7795338441890166</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.7694248454193424</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.8464862423253259</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7975902673577345</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.7795338441890166</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ajeric_expert2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.9073682562054655</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.8820164784298342</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.8419125803468687</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8985954991316421</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9073682562054655</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ekamis_expert2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.9196710478008664</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.8935878438314061</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7406111089041645</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9051757788652476</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9196710478008664</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>iguted_expert1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9112295393985534</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8909245446310579</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7745438971790324</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9038569525773893</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9112295393985534</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>inefoh_expert1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.9455034761157211</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9315076195846097</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8066273588849397</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9366791704551629</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9455034761157211</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>otafeh_expert1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.9558798859251804</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9417714590840834</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7466403563474648</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9497625134228358</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9558798859251804</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>oxused_expert2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.8613853103563661</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8250184182772685</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8815522431827741</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.8631062196166285</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8613853103563661</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pqbqpr_expert2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.9398628795298727</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9287233773454189</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.8037949477321206</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9264148515218237</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9398628795298727</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>uhepah_expert1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.9440385254068416</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9345635079282449</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8731265908300477</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9377846145718652</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9440385254068416</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ukudab_expert2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.8964817793942785</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.8650891221903191</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.8019052814783563</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.8749781057630956</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.8964817793942785</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>true_negative</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>false_positive</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>false_negative</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>true_positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>afegip_expert1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>6757</v>
+      </c>
+      <c r="C2" t="n">
+        <v>398</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2430</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2943</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ajeric_expert2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>11299</v>
+      </c>
+      <c r="C3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1131</v>
+      </c>
+      <c r="E3" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ekamis_expert2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>12369</v>
+      </c>
+      <c r="C4" t="n">
+        <v>59</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1045</v>
+      </c>
+      <c r="E4" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>iguted_expert1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>11580</v>
+      </c>
+      <c r="C5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1125</v>
+      </c>
+      <c r="E5" t="n">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>inefoh_expert1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>12478</v>
+      </c>
+      <c r="C6" t="n">
+        <v>39</v>
+      </c>
+      <c r="D6" t="n">
+        <v>689</v>
+      </c>
+      <c r="E6" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>otafeh_expert1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>11304</v>
+      </c>
+      <c r="C7" t="n">
+        <v>17</v>
+      </c>
+      <c r="D7" t="n">
+        <v>517</v>
+      </c>
+      <c r="E7" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>oxused_expert2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>9861</v>
+      </c>
+      <c r="C8" t="n">
+        <v>49</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1672</v>
+      </c>
+      <c r="E8" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pqbqpr_expert2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>14229</v>
+      </c>
+      <c r="C9" t="n">
+        <v>96</v>
+      </c>
+      <c r="D9" t="n">
+        <v>767</v>
+      </c>
+      <c r="E9" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>uhepah_expert1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>11052</v>
+      </c>
+      <c r="C10" t="n">
+        <v>56</v>
+      </c>
+      <c r="D10" t="n">
+        <v>671</v>
+      </c>
+      <c r="E10" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ukudab_expert2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>12606</v>
+      </c>
+      <c r="C11" t="n">
+        <v>107</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1381</v>
+      </c>
+      <c r="E11" t="n">
+        <v>203</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>acc</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>roc_auc</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>prec</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>rec</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>afegip_expert1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.7742656449553001</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.7619805281240067</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.8640933658639238</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7978455030996335</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.7742656449553001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ajeric_expert2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.9058805105316733</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.8793407831752361</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.8418356155955948</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8961510532927121</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9058805105316733</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ekamis_expert2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.918936779499229</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.8918556334227971</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7043655249366494</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9037401733905115</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.918936779499229</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>iguted_expert1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9086410354015988</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8854982213192496</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7795843913411481</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9017766023393871</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9086410354015988</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>inefoh_expert1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.9455782312925171</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9297368965707314</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.7605782182743097</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9390968660571238</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9455782312925171</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>otafeh_expert1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.9552088575742325</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9397414688814231</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7640442915195518</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9499840166446412</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9552088575742325</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>oxused_expert2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.8560314539066421</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8140841438583309</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8857528914832316</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.8599125527343391</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8560314539066421</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pqbqpr_expert2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.9436500163238655</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.92985214748536</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7919648139334003</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9327057514908385</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9436500163238655</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>uhepah_expert1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.9396379940219196</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9256846196437281</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8703236906333773</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9336525734000952</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9396379940219196</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ukudab_expert2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.8959222214450584</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.8634012919620628</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.7989488410415807</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.8739632313834319</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.8959222214450584</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>true_negative</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>false_positive</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>false_negative</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>true_positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>afegip_expert1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>6880</v>
+      </c>
+      <c r="C2" t="n">
+        <v>275</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2827</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2546</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ajeric_expert2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>11322</v>
+      </c>
+      <c r="C3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1178</v>
+      </c>
+      <c r="E3" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ekamis_expert2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>12372</v>
+      </c>
+      <c r="C4" t="n">
+        <v>56</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1041</v>
+      </c>
+      <c r="E4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>iguted_expert1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>11572</v>
+      </c>
+      <c r="C5" t="n">
+        <v>83</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1115</v>
+      </c>
+      <c r="E5" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>inefoh_expert1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>12485</v>
+      </c>
+      <c r="C6" t="n">
+        <v>32</v>
+      </c>
+      <c r="D6" t="n">
+        <v>706</v>
+      </c>
+      <c r="E6" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>otafeh_expert1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>11303</v>
+      </c>
+      <c r="C7" t="n">
+        <v>18</v>
+      </c>
+      <c r="D7" t="n">
+        <v>518</v>
+      </c>
+      <c r="E7" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>oxused_expert2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>9864</v>
+      </c>
+      <c r="C8" t="n">
+        <v>46</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1635</v>
+      </c>
+      <c r="E8" t="n">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pqbqpr_expert2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>14260</v>
+      </c>
+      <c r="C9" t="n">
+        <v>65</v>
+      </c>
+      <c r="D9" t="n">
+        <v>778</v>
+      </c>
+      <c r="E9" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>uhepah_expert1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>11086</v>
+      </c>
+      <c r="C10" t="n">
+        <v>22</v>
+      </c>
+      <c r="D10" t="n">
+        <v>756</v>
+      </c>
+      <c r="E10" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ukudab_expert2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>12607</v>
+      </c>
+      <c r="C11" t="n">
+        <v>106</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1395</v>
+      </c>
+      <c r="E11" t="n">
+        <v>189</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>acc</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>roc_auc</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>prec</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>rec</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>afegip_expert1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.7523946360153256</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.7325736807563517</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.8570816658024184</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7918622222383296</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.7523946360153256</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ajeric_expert2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.9040012528384621</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.8738337634906873</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.8306297424191917</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.896667731463784</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9040012528384621</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ekamis_expert2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.9194507673103752</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.8925890239558589</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7187534202041543</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9054027544801372</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9194507673103752</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>iguted_expert1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9087933003425961</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8863166017152544</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7816514777325587</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9011420735336587</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9087933003425961</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>inefoh_expert1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.9448306795245571</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9277794439988689</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.749330352580955</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9388589664439064</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9448306795245571</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>otafeh_expert1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.9550411004864956</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9395157814989564</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7280242524861767</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9494045671023201</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9550411004864956</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>oxused_expert2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.8593776141877196</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.819888512529367</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8921426399236968</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.8648392036485039</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8593776141877196</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pqbqpr_expert2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.9449559255631733</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9301362887010052</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7869567578049255</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9364398965539552</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9449559255631733</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>uhepah_expert1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.935403520425108</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9156044203189351</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8518890577823328</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.932656790307608</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.935403520425108</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ukudab_expert2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.8950129397775757</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.8615350257836292</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.8078556547938284</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.8715993002212116</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.8950129397775757</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/server-side/modelling/results/taylor svm tables.xlsx
+++ b/server-side/modelling/results/taylor svm tables.xlsx
@@ -23,8 +23,10 @@
     <sheet name="taylor svm 100 0p1 metrics" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="taylor svm 100 0p01 cm" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="taylor svm 100 0p01 metrics" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="taylor svm 1000 0p001 cm" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="taylor svm 1000 0p001 metrics" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="taylor svm 100 0p001 cm" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="taylor svm 100 0p001 metrics" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="taylor svm 1000 0p001 cm" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="taylor svm 1000 0p001 metrics" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2422,16 +2424,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6880</v>
+        <v>7042</v>
       </c>
       <c r="C2" t="n">
-        <v>275</v>
+        <v>113</v>
       </c>
       <c r="D2" t="n">
-        <v>2827</v>
+        <v>3418</v>
       </c>
       <c r="E2" t="n">
-        <v>2546</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="3">
@@ -2441,16 +2443,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11322</v>
+        <v>11346</v>
       </c>
       <c r="C3" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>1178</v>
+        <v>1257</v>
       </c>
       <c r="E3" t="n">
-        <v>223</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4">
@@ -2460,16 +2462,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12372</v>
+        <v>12389</v>
       </c>
       <c r="C4" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="D4" t="n">
-        <v>1041</v>
+        <v>1098</v>
       </c>
       <c r="E4" t="n">
-        <v>150</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5">
@@ -2479,16 +2481,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11572</v>
+        <v>11588</v>
       </c>
       <c r="C5" t="n">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D5" t="n">
-        <v>1115</v>
+        <v>1153</v>
       </c>
       <c r="E5" t="n">
-        <v>365</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6">
@@ -2498,16 +2500,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12485</v>
+        <v>12493</v>
       </c>
       <c r="C6" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>706</v>
+        <v>722</v>
       </c>
       <c r="E6" t="n">
-        <v>154</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7">
@@ -2517,16 +2519,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11303</v>
+        <v>11307</v>
       </c>
       <c r="C7" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E7" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -2536,16 +2538,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9864</v>
+        <v>9874</v>
       </c>
       <c r="C8" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>1635</v>
+        <v>1699</v>
       </c>
       <c r="E8" t="n">
-        <v>409</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -2555,16 +2557,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14260</v>
+        <v>14263</v>
       </c>
       <c r="C9" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D9" t="n">
-        <v>778</v>
+        <v>802</v>
       </c>
       <c r="E9" t="n">
-        <v>212</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -2574,16 +2576,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11086</v>
+        <v>11104</v>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>756</v>
+        <v>830</v>
       </c>
       <c r="E10" t="n">
-        <v>180</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11">
@@ -2593,16 +2595,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12607</v>
+        <v>12649</v>
       </c>
       <c r="C11" t="n">
-        <v>106</v>
+        <v>64</v>
       </c>
       <c r="D11" t="n">
-        <v>1395</v>
+        <v>1495</v>
       </c>
       <c r="E11" t="n">
-        <v>189</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -2653,19 +2655,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7523946360153256</v>
+        <v>0.7181513409961686</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7325736807563517</v>
+        <v>0.6819991000962641</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8570816658024184</v>
+        <v>0.8551921290850036</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7918622222383296</v>
+        <v>0.7899407729502577</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7523946360153256</v>
+        <v>0.7181513409961686</v>
       </c>
     </row>
     <row r="3">
@@ -2675,19 +2677,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9040012528384621</v>
+        <v>0.8996946206248532</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8738337634906873</v>
+        <v>0.8628615826475747</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8306297424191917</v>
+        <v>0.8158938175207181</v>
       </c>
       <c r="E3" t="n">
-        <v>0.896667731463784</v>
+        <v>0.8955316178181166</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9040012528384621</v>
+        <v>0.8996946206248532</v>
       </c>
     </row>
     <row r="4">
@@ -2697,19 +2699,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9194507673103752</v>
+        <v>0.9165136941038255</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8925890239558589</v>
+        <v>0.884806048017989</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7187534202041543</v>
+        <v>0.7145757379466262</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9054027544801372</v>
+        <v>0.8998699359891733</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9194507673103752</v>
+        <v>0.9165136941038255</v>
       </c>
     </row>
     <row r="5">
@@ -2719,19 +2721,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9087933003425961</v>
+        <v>0.9071183859916254</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8863166017152544</v>
+        <v>0.88227285252619</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7816514777325587</v>
+        <v>0.7998443713984255</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9011420735336587</v>
+        <v>0.9005407473376376</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9087933003425961</v>
+        <v>0.9071183859916254</v>
       </c>
     </row>
     <row r="6">
@@ -2741,19 +2743,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9448306795245571</v>
+        <v>0.9442326381101891</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9277794439988689</v>
+        <v>0.9259451593705914</v>
       </c>
       <c r="D6" t="n">
-        <v>0.749330352580955</v>
+        <v>0.7726891892142964</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9388589664439064</v>
+        <v>0.9393531989268127</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9448306795245571</v>
+        <v>0.9442326381101891</v>
       </c>
     </row>
     <row r="7">
@@ -2763,19 +2765,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9550411004864956</v>
+        <v>0.9548733433987586</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9395157814989564</v>
+        <v>0.9387413334079683</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7280242524861767</v>
+        <v>0.7342583783674149</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9494045671023201</v>
+        <v>0.9501867620789289</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9550411004864956</v>
+        <v>0.9548733433987586</v>
       </c>
     </row>
     <row r="8">
@@ -2785,19 +2787,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8593776141877196</v>
+        <v>0.854860297808265</v>
       </c>
       <c r="C8" t="n">
-        <v>0.819888512529367</v>
+        <v>0.8107114745479892</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8921426399236968</v>
+        <v>0.8876883388855867</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8648392036485039</v>
+        <v>0.8621387447517662</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8593776141877196</v>
+        <v>0.854860297808265</v>
       </c>
     </row>
     <row r="9">
@@ -2807,19 +2809,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9449559255631733</v>
+        <v>0.9435847208619002</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9301362887010052</v>
+        <v>0.9274613592877725</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7869567578049255</v>
+        <v>0.7806410703897615</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9364398965539552</v>
+        <v>0.9341739878092744</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9449559255631733</v>
+        <v>0.9435847208619002</v>
       </c>
     </row>
     <row r="10">
@@ -2829,19 +2831,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.935403520425108</v>
+        <v>0.9307539023580206</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9156044203189351</v>
+        <v>0.904654100540402</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8518890577823328</v>
+        <v>0.855017866541093</v>
       </c>
       <c r="E10" t="n">
-        <v>0.932656790307608</v>
+        <v>0.9330298293746044</v>
       </c>
       <c r="F10" t="n">
-        <v>0.935403520425108</v>
+        <v>0.9307539023580206</v>
       </c>
     </row>
     <row r="11">
@@ -2851,19 +2853,245 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8950129397775757</v>
+        <v>0.8909561446457299</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8615350257836292</v>
+        <v>0.8489441643075906</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8078556547938284</v>
+        <v>0.7954712308326718</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8715993002212116</v>
+        <v>0.8596675078893556</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8950129397775757</v>
+        <v>0.8909561446457299</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>true_negative</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>false_positive</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>false_negative</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>true_positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>afegip_expert1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>6880</v>
+      </c>
+      <c r="C2" t="n">
+        <v>275</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2827</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2546</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ajeric_expert2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>11322</v>
+      </c>
+      <c r="C3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1178</v>
+      </c>
+      <c r="E3" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ekamis_expert2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>12372</v>
+      </c>
+      <c r="C4" t="n">
+        <v>56</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1041</v>
+      </c>
+      <c r="E4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>iguted_expert1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>11572</v>
+      </c>
+      <c r="C5" t="n">
+        <v>83</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1115</v>
+      </c>
+      <c r="E5" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>inefoh_expert1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>12485</v>
+      </c>
+      <c r="C6" t="n">
+        <v>32</v>
+      </c>
+      <c r="D6" t="n">
+        <v>706</v>
+      </c>
+      <c r="E6" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>otafeh_expert1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>11303</v>
+      </c>
+      <c r="C7" t="n">
+        <v>18</v>
+      </c>
+      <c r="D7" t="n">
+        <v>518</v>
+      </c>
+      <c r="E7" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>oxused_expert2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>9864</v>
+      </c>
+      <c r="C8" t="n">
+        <v>46</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1635</v>
+      </c>
+      <c r="E8" t="n">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pqbqpr_expert2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>14260</v>
+      </c>
+      <c r="C9" t="n">
+        <v>65</v>
+      </c>
+      <c r="D9" t="n">
+        <v>778</v>
+      </c>
+      <c r="E9" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>uhepah_expert1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>11086</v>
+      </c>
+      <c r="C10" t="n">
+        <v>22</v>
+      </c>
+      <c r="D10" t="n">
+        <v>756</v>
+      </c>
+      <c r="E10" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ukudab_expert2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>12607</v>
+      </c>
+      <c r="C11" t="n">
+        <v>106</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1395</v>
+      </c>
+      <c r="E11" t="n">
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -3132,6 +3360,267 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>acc</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>roc_auc</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>prec</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>rec</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>afegip_expert1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.7523946360153256</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.7325736807563517</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.8570816658024184</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7918622222383296</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.7523946360153256</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ajeric_expert2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.9040012528384621</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.8738337634906873</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.8306297424191917</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.896667731463784</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9040012528384621</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ekamis_expert2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.9194507673103752</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.8925890239558589</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7187534202041543</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9054027544801372</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9194507673103752</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>iguted_expert1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9087933003425961</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8863166017152544</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7816514777325587</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9011420735336587</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9087933003425961</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>inefoh_expert1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.9448306795245571</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9277794439988689</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.749330352580955</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9388589664439064</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9448306795245571</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>otafeh_expert1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.9550411004864956</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9395157814989564</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7280242524861767</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9494045671023201</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9550411004864956</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>oxused_expert2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.8593776141877196</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.819888512529367</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8921426399236968</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.8648392036485039</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8593776141877196</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pqbqpr_expert2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.9449559255631733</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9301362887010052</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7869567578049255</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9364398965539552</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9449559255631733</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>uhepah_expert1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.935403520425108</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9156044203189351</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8518890577823328</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.932656790307608</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.935403520425108</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ukudab_expert2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.8950129397775757</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.8615350257836292</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.8078556547938284</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.8715993002212116</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.8950129397775757</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/server-side/modelling/results/taylor svm tables.xlsx
+++ b/server-side/modelling/results/taylor svm tables.xlsx
@@ -17,16 +17,20 @@
     <sheet name="taylor svm 1 0p001 metrics" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="taylor svm 10 0p1 cm" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="taylor svm 10 0p1 metrics" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="taylor svm 10 0p001 cm" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="taylor svm 10 0p001 metrics" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="taylor svm 100 0p1 cm" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="taylor svm 100 0p1 metrics" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="taylor svm 100 0p01 cm" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="taylor svm 100 0p01 metrics" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="taylor svm 100 0p001 cm" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="taylor svm 100 0p001 metrics" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="taylor svm 1000 0p001 cm" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="taylor svm 1000 0p001 metrics" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="taylor svm 10 0p01 cm" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="taylor svm 10 0p01 metrics" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="taylor svm 10 0p001 cm" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="taylor svm 10 0p001 metrics" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="taylor svm 100 0p1 cm" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="taylor svm 100 0p1 metrics" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="taylor svm 100 0p01 cm" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="taylor svm 100 0p01 metrics" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="taylor svm 100 0p001 cm" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="taylor svm 100 0p001 metrics" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="taylor svm 1000 0p1 cm" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="taylor svm 1000 0p1 metrics" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="taylor svm 1000 0p001 cm" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="taylor svm 1000 0p001 metrics" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -963,16 +967,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7128</v>
+        <v>6980</v>
       </c>
       <c r="C2" t="n">
-        <v>27</v>
+        <v>175</v>
       </c>
       <c r="D2" t="n">
-        <v>4122</v>
+        <v>3017</v>
       </c>
       <c r="E2" t="n">
-        <v>1251</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="3">
@@ -982,16 +986,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11357</v>
+        <v>11326</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="D3" t="n">
-        <v>1324</v>
+        <v>1228</v>
       </c>
       <c r="E3" t="n">
-        <v>77</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4">
@@ -1001,16 +1005,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12408</v>
+        <v>12385</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="D4" t="n">
-        <v>1142</v>
+        <v>1095</v>
       </c>
       <c r="E4" t="n">
-        <v>49</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5">
@@ -1020,16 +1024,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11619</v>
+        <v>11598</v>
       </c>
       <c r="C5" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D5" t="n">
-        <v>1257</v>
+        <v>1169</v>
       </c>
       <c r="E5" t="n">
-        <v>223</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6">
@@ -1039,16 +1043,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12498</v>
+        <v>12488</v>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D6" t="n">
-        <v>765</v>
+        <v>718</v>
       </c>
       <c r="E6" t="n">
-        <v>95</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7">
@@ -1058,16 +1062,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11313</v>
+        <v>11308</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>543</v>
+        <v>526</v>
       </c>
       <c r="E7" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8">
@@ -1077,16 +1081,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9889</v>
+        <v>9874</v>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>1828</v>
+        <v>1785</v>
       </c>
       <c r="E8" t="n">
-        <v>216</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9">
@@ -1096,16 +1100,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14271</v>
+        <v>14243</v>
       </c>
       <c r="C9" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="D9" t="n">
-        <v>859</v>
+        <v>800</v>
       </c>
       <c r="E9" t="n">
-        <v>131</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10">
@@ -1115,16 +1119,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11108</v>
+        <v>11092</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>893</v>
+        <v>767</v>
       </c>
       <c r="E10" t="n">
-        <v>43</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -1134,16 +1138,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12691</v>
+        <v>12646</v>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="D11" t="n">
-        <v>1551</v>
+        <v>1475</v>
       </c>
       <c r="E11" t="n">
-        <v>33</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -1194,19 +1198,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6688218390804598</v>
+        <v>0.7452107279693486</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6037117158506877</v>
+        <v>0.7205127534987529</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8541745401698556</v>
+        <v>0.8631653102065963</v>
       </c>
       <c r="E2" t="n">
-        <v>0.781680548810102</v>
+        <v>0.7979873362272991</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6688218390804598</v>
+        <v>0.7452107279693486</v>
       </c>
     </row>
     <row r="3">
@@ -1216,19 +1220,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8953096860073604</v>
+        <v>0.9003993422598073</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8521371548173298</v>
+        <v>0.8664216952662266</v>
       </c>
       <c r="D3" t="n">
-        <v>0.793344652048386</v>
+        <v>0.8188565837820327</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8911997841839777</v>
+        <v>0.8906696502130887</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8953096860073604</v>
+        <v>0.9003993422598073</v>
       </c>
     </row>
     <row r="4">
@@ -1238,19 +1242,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.914678023349732</v>
+        <v>0.9164402672736618</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8785319737873433</v>
+        <v>0.8850898159845249</v>
       </c>
       <c r="D4" t="n">
-        <v>0.707807077920797</v>
+        <v>0.7088767826610748</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8977417773347691</v>
+        <v>0.8988190499077304</v>
       </c>
       <c r="F4" t="n">
-        <v>0.914678023349732</v>
+        <v>0.9164402672736618</v>
       </c>
     </row>
     <row r="5">
@@ -1260,19 +1264,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9015607156452227</v>
+        <v>0.9066615911686334</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8694520899213385</v>
+        <v>0.880704231693469</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8261449673611836</v>
+        <v>0.7939307454172319</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8977148070154384</v>
+        <v>0.9013003614502734</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9015607156452227</v>
+        <v>0.9066615911686334</v>
       </c>
     </row>
     <row r="6">
@@ -1282,19 +1286,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9413919413919414</v>
+        <v>0.9441578829333931</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9197955575938286</v>
+        <v>0.926246583830974</v>
       </c>
       <c r="D6" t="n">
-        <v>0.78698848635623</v>
+        <v>0.7652711382287531</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9353140011362132</v>
+        <v>0.9382232521172882</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9413919413919414</v>
+        <v>0.9441578829333931</v>
       </c>
     </row>
     <row r="7">
@@ -1304,19 +1308,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9537829223284684</v>
+        <v>0.9547894648548901</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9357810072754044</v>
+        <v>0.9384593678541944</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7731339767172487</v>
+        <v>0.7659268824549845</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9503987836396851</v>
+        <v>0.9503453980660066</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9537829223284684</v>
+        <v>0.9547894648548901</v>
       </c>
     </row>
     <row r="8">
@@ -1326,19 +1330,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8453237410071942</v>
+        <v>0.8476660532039485</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7905185829638657</v>
+        <v>0.7968880568475517</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8711127643902756</v>
+        <v>0.8766794250011354</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8555128743987935</v>
+        <v>0.8522114503058184</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8453237410071942</v>
+        <v>0.8476660532039485</v>
       </c>
     </row>
     <row r="9">
@@ -1348,19 +1352,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9403852432255958</v>
+        <v>0.9424094025465231</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9207786484723729</v>
+        <v>0.9267306556942443</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7823548574752763</v>
+        <v>0.7930910853738078</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9280268100617109</v>
+        <v>0.9307690493336437</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9403852432255958</v>
+        <v>0.9424094025465231</v>
       </c>
     </row>
     <row r="10">
@@ -1370,19 +1374,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9258551976087679</v>
+        <v>0.9349883759548323</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8934719988955298</v>
+        <v>0.9142744221734374</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8639466165911071</v>
+        <v>0.8759625772139277</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9313723468909418</v>
+        <v>0.9336284280930032</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9258551976087679</v>
+        <v>0.9349883759548323</v>
       </c>
     </row>
     <row r="11">
@@ -1392,19 +1396,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8899769182345947</v>
+        <v>0.8921452052878226</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8417779110677597</v>
+        <v>0.8518328981757538</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7723118266754703</v>
+        <v>0.7785678006367457</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8588454263106587</v>
+        <v>0.8649417176420996</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8899769182345947</v>
+        <v>0.8921452052878226</v>
       </c>
     </row>
   </sheetData>
@@ -1450,16 +1454,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6688</v>
+        <v>7128</v>
       </c>
       <c r="C2" t="n">
-        <v>467</v>
+        <v>27</v>
       </c>
       <c r="D2" t="n">
-        <v>2295</v>
+        <v>4122</v>
       </c>
       <c r="E2" t="n">
-        <v>3078</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="3">
@@ -1469,16 +1473,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11299</v>
+        <v>11357</v>
       </c>
       <c r="C3" t="n">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>1112</v>
+        <v>1324</v>
       </c>
       <c r="E3" t="n">
-        <v>289</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4">
@@ -1488,16 +1492,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12366</v>
+        <v>12408</v>
       </c>
       <c r="C4" t="n">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>1032</v>
+        <v>1142</v>
       </c>
       <c r="E4" t="n">
-        <v>159</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
@@ -1507,16 +1511,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11564</v>
+        <v>11619</v>
       </c>
       <c r="C5" t="n">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="D5" t="n">
-        <v>1075</v>
+        <v>1257</v>
       </c>
       <c r="E5" t="n">
-        <v>405</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6">
@@ -1526,16 +1530,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12453</v>
+        <v>12498</v>
       </c>
       <c r="C6" t="n">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>665</v>
+        <v>765</v>
       </c>
       <c r="E6" t="n">
-        <v>195</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7">
@@ -1545,16 +1549,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11297</v>
+        <v>11313</v>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>502</v>
+        <v>543</v>
       </c>
       <c r="E7" t="n">
-        <v>99</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8">
@@ -1564,16 +1568,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9845</v>
+        <v>9889</v>
       </c>
       <c r="C8" t="n">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>1592</v>
+        <v>1828</v>
       </c>
       <c r="E8" t="n">
-        <v>452</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9">
@@ -1583,16 +1587,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14142</v>
+        <v>14271</v>
       </c>
       <c r="C9" t="n">
-        <v>183</v>
+        <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>738</v>
+        <v>859</v>
       </c>
       <c r="E9" t="n">
-        <v>252</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10">
@@ -1602,16 +1606,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11019</v>
+        <v>11108</v>
       </c>
       <c r="C10" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>585</v>
+        <v>893</v>
       </c>
       <c r="E10" t="n">
-        <v>351</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">
@@ -1621,16 +1625,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12599</v>
+        <v>12691</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
-        <v>1366</v>
+        <v>1551</v>
       </c>
       <c r="E11" t="n">
-        <v>218</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1681,19 +1685,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7795338441890166</v>
+        <v>0.6688218390804598</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7694248454193424</v>
+        <v>0.6037117158506877</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8464862423253259</v>
+        <v>0.8541745401698556</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7975902673577345</v>
+        <v>0.781680548810102</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7795338441890166</v>
+        <v>0.6688218390804598</v>
       </c>
     </row>
     <row r="3">
@@ -1703,19 +1707,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9073682562054655</v>
+        <v>0.8953096860073604</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8820164784298342</v>
+        <v>0.8521371548173298</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8419125803468687</v>
+        <v>0.793344652048386</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8985954991316421</v>
+        <v>0.8911997841839777</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9073682562054655</v>
+        <v>0.8953096860073604</v>
       </c>
     </row>
     <row r="4">
@@ -1725,19 +1729,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9196710478008664</v>
+        <v>0.914678023349732</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8935878438314061</v>
+        <v>0.8785319737873433</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7406111089041645</v>
+        <v>0.707807077920797</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9051757788652476</v>
+        <v>0.8977417773347691</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9196710478008664</v>
+        <v>0.914678023349732</v>
       </c>
     </row>
     <row r="5">
@@ -1747,19 +1751,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9112295393985534</v>
+        <v>0.9015607156452227</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8909245446310579</v>
+        <v>0.8694520899213385</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7745438971790324</v>
+        <v>0.8261449673611836</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9038569525773893</v>
+        <v>0.8977148070154384</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9112295393985534</v>
+        <v>0.9015607156452227</v>
       </c>
     </row>
     <row r="6">
@@ -1769,19 +1773,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9455034761157211</v>
+        <v>0.9413919413919414</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9315076195846097</v>
+        <v>0.9197955575938286</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8066273588849397</v>
+        <v>0.78698848635623</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9366791704551629</v>
+        <v>0.9353140011362132</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9455034761157211</v>
+        <v>0.9413919413919414</v>
       </c>
     </row>
     <row r="7">
@@ -1791,19 +1795,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9558798859251804</v>
+        <v>0.9537829223284684</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9417714590840834</v>
+        <v>0.9357810072754044</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7466403563474648</v>
+        <v>0.7731339767172487</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9497625134228358</v>
+        <v>0.9503987836396851</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9558798859251804</v>
+        <v>0.9537829223284684</v>
       </c>
     </row>
     <row r="8">
@@ -1813,19 +1817,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8613853103563661</v>
+        <v>0.8453237410071942</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8250184182772685</v>
+        <v>0.7905185829638657</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8815522431827741</v>
+        <v>0.8711127643902756</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8631062196166285</v>
+        <v>0.8555128743987935</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8613853103563661</v>
+        <v>0.8453237410071942</v>
       </c>
     </row>
     <row r="9">
@@ -1835,19 +1839,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9398628795298727</v>
+        <v>0.9403852432255958</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9287233773454189</v>
+        <v>0.9207786484723729</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8037949477321206</v>
+        <v>0.7823548574752763</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9264148515218237</v>
+        <v>0.9280268100617109</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9398628795298727</v>
+        <v>0.9403852432255958</v>
       </c>
     </row>
     <row r="10">
@@ -1857,19 +1861,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9440385254068416</v>
+        <v>0.9258551976087679</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9345635079282449</v>
+        <v>0.8934719988955298</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8731265908300477</v>
+        <v>0.8639466165911071</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9377846145718652</v>
+        <v>0.9313723468909418</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9440385254068416</v>
+        <v>0.9258551976087679</v>
       </c>
     </row>
     <row r="11">
@@ -1879,19 +1883,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8964817793942785</v>
+        <v>0.8899769182345947</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8650891221903191</v>
+        <v>0.8417779110677597</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8019052814783563</v>
+        <v>0.7723118266754703</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8749781057630956</v>
+        <v>0.8588454263106587</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8964817793942785</v>
+        <v>0.8899769182345947</v>
       </c>
     </row>
   </sheetData>
@@ -1937,16 +1941,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6757</v>
+        <v>6688</v>
       </c>
       <c r="C2" t="n">
-        <v>398</v>
+        <v>467</v>
       </c>
       <c r="D2" t="n">
-        <v>2430</v>
+        <v>2295</v>
       </c>
       <c r="E2" t="n">
-        <v>2943</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="3">
@@ -1962,10 +1966,10 @@
         <v>71</v>
       </c>
       <c r="D3" t="n">
-        <v>1131</v>
+        <v>1112</v>
       </c>
       <c r="E3" t="n">
-        <v>270</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4">
@@ -1975,16 +1979,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12369</v>
+        <v>12366</v>
       </c>
       <c r="C4" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D4" t="n">
-        <v>1045</v>
+        <v>1032</v>
       </c>
       <c r="E4" t="n">
-        <v>146</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5">
@@ -1994,16 +1998,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11580</v>
+        <v>11564</v>
       </c>
       <c r="C5" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="D5" t="n">
-        <v>1125</v>
+        <v>1075</v>
       </c>
       <c r="E5" t="n">
-        <v>355</v>
+        <v>405</v>
       </c>
     </row>
     <row r="6">
@@ -2013,16 +2017,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12478</v>
+        <v>12453</v>
       </c>
       <c r="C6" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="D6" t="n">
-        <v>689</v>
+        <v>665</v>
       </c>
       <c r="E6" t="n">
-        <v>171</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7">
@@ -2032,16 +2036,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11304</v>
+        <v>11297</v>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>502</v>
       </c>
       <c r="E7" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8">
@@ -2051,16 +2055,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9861</v>
+        <v>9845</v>
       </c>
       <c r="C8" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D8" t="n">
-        <v>1672</v>
+        <v>1592</v>
       </c>
       <c r="E8" t="n">
-        <v>372</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -2070,16 +2074,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14229</v>
+        <v>14142</v>
       </c>
       <c r="C9" t="n">
-        <v>96</v>
+        <v>183</v>
       </c>
       <c r="D9" t="n">
-        <v>767</v>
+        <v>738</v>
       </c>
       <c r="E9" t="n">
-        <v>223</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10">
@@ -2089,16 +2093,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11052</v>
+        <v>11019</v>
       </c>
       <c r="C10" t="n">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="D10" t="n">
-        <v>671</v>
+        <v>585</v>
       </c>
       <c r="E10" t="n">
-        <v>265</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11">
@@ -2108,16 +2112,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12606</v>
+        <v>12599</v>
       </c>
       <c r="C11" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>1381</v>
+        <v>1366</v>
       </c>
       <c r="E11" t="n">
-        <v>203</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -2168,19 +2172,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7742656449553001</v>
+        <v>0.7795338441890166</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7619805281240067</v>
+        <v>0.7694248454193424</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8640933658639238</v>
+        <v>0.8464862423253259</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7978455030996335</v>
+        <v>0.7975902673577345</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7742656449553001</v>
+        <v>0.7795338441890166</v>
       </c>
     </row>
     <row r="3">
@@ -2190,19 +2194,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9058805105316733</v>
+        <v>0.9073682562054655</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8793407831752361</v>
+        <v>0.8820164784298342</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8418356155955948</v>
+        <v>0.8419125803468687</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8961510532927121</v>
+        <v>0.8985954991316421</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9058805105316733</v>
+        <v>0.9073682562054655</v>
       </c>
     </row>
     <row r="4">
@@ -2212,19 +2216,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.918936779499229</v>
+        <v>0.9196710478008664</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8918556334227971</v>
+        <v>0.8935878438314061</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7043655249366494</v>
+        <v>0.7406111089041645</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9037401733905115</v>
+        <v>0.9051757788652476</v>
       </c>
       <c r="F4" t="n">
-        <v>0.918936779499229</v>
+        <v>0.9196710478008664</v>
       </c>
     </row>
     <row r="5">
@@ -2234,19 +2238,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9086410354015988</v>
+        <v>0.9112295393985534</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8854982213192496</v>
+        <v>0.8909245446310579</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7795843913411481</v>
+        <v>0.7745438971790324</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9017766023393871</v>
+        <v>0.9038569525773893</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9086410354015988</v>
+        <v>0.9112295393985534</v>
       </c>
     </row>
     <row r="6">
@@ -2256,19 +2260,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9455782312925171</v>
+        <v>0.9455034761157211</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9297368965707314</v>
+        <v>0.9315076195846097</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7605782182743097</v>
+        <v>0.8066273588849397</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9390968660571238</v>
+        <v>0.9366791704551629</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9455782312925171</v>
+        <v>0.9455034761157211</v>
       </c>
     </row>
     <row r="7">
@@ -2278,19 +2282,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9552088575742325</v>
+        <v>0.9558798859251804</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9397414688814231</v>
+        <v>0.9417714590840834</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7640442915195518</v>
+        <v>0.7466403563474648</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9499840166446412</v>
+        <v>0.9497625134228358</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9552088575742325</v>
+        <v>0.9558798859251804</v>
       </c>
     </row>
     <row r="8">
@@ -2300,19 +2304,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8560314539066421</v>
+        <v>0.8613853103563661</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8140841438583309</v>
+        <v>0.8250184182772685</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8857528914832316</v>
+        <v>0.8815522431827741</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8599125527343391</v>
+        <v>0.8631062196166285</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8560314539066421</v>
+        <v>0.8613853103563661</v>
       </c>
     </row>
     <row r="9">
@@ -2322,19 +2326,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9436500163238655</v>
+        <v>0.9398628795298727</v>
       </c>
       <c r="C9" t="n">
-        <v>0.92985214748536</v>
+        <v>0.9287233773454189</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7919648139334003</v>
+        <v>0.8037949477321206</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9327057514908385</v>
+        <v>0.9264148515218237</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9436500163238655</v>
+        <v>0.9398628795298727</v>
       </c>
     </row>
     <row r="10">
@@ -2344,19 +2348,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9396379940219196</v>
+        <v>0.9440385254068416</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9256846196437281</v>
+        <v>0.9345635079282449</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8703236906333773</v>
+        <v>0.8731265908300477</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9336525734000952</v>
+        <v>0.9377846145718652</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9396379940219196</v>
+        <v>0.9440385254068416</v>
       </c>
     </row>
     <row r="11">
@@ -2366,19 +2370,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8959222214450584</v>
+        <v>0.8964817793942785</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8634012919620628</v>
+        <v>0.8650891221903191</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7989488410415807</v>
+        <v>0.8019052814783563</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8739632313834319</v>
+        <v>0.8749781057630956</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8959222214450584</v>
+        <v>0.8964817793942785</v>
       </c>
     </row>
   </sheetData>
@@ -2424,16 +2428,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7042</v>
+        <v>6757</v>
       </c>
       <c r="C2" t="n">
-        <v>113</v>
+        <v>398</v>
       </c>
       <c r="D2" t="n">
-        <v>3418</v>
+        <v>2430</v>
       </c>
       <c r="E2" t="n">
-        <v>1955</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="3">
@@ -2443,16 +2447,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11346</v>
+        <v>11299</v>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D3" t="n">
-        <v>1257</v>
+        <v>1131</v>
       </c>
       <c r="E3" t="n">
-        <v>144</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4">
@@ -2462,16 +2466,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12389</v>
+        <v>12369</v>
       </c>
       <c r="C4" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="D4" t="n">
-        <v>1098</v>
+        <v>1045</v>
       </c>
       <c r="E4" t="n">
-        <v>93</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5">
@@ -2481,16 +2485,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11588</v>
+        <v>11580</v>
       </c>
       <c r="C5" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D5" t="n">
-        <v>1153</v>
+        <v>1125</v>
       </c>
       <c r="E5" t="n">
-        <v>327</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6">
@@ -2500,16 +2504,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12493</v>
+        <v>12478</v>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D6" t="n">
-        <v>722</v>
+        <v>689</v>
       </c>
       <c r="E6" t="n">
-        <v>138</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7">
@@ -2519,16 +2523,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11307</v>
+        <v>11304</v>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="E7" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">
@@ -2538,16 +2542,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9874</v>
+        <v>9861</v>
       </c>
       <c r="C8" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D8" t="n">
-        <v>1699</v>
+        <v>1672</v>
       </c>
       <c r="E8" t="n">
-        <v>345</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -2557,16 +2561,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14263</v>
+        <v>14229</v>
       </c>
       <c r="C9" t="n">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="D9" t="n">
-        <v>802</v>
+        <v>767</v>
       </c>
       <c r="E9" t="n">
-        <v>188</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10">
@@ -2576,16 +2580,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11104</v>
+        <v>11052</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="D10" t="n">
-        <v>830</v>
+        <v>671</v>
       </c>
       <c r="E10" t="n">
-        <v>106</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11">
@@ -2595,16 +2599,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12649</v>
+        <v>12606</v>
       </c>
       <c r="C11" t="n">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="D11" t="n">
-        <v>1495</v>
+        <v>1381</v>
       </c>
       <c r="E11" t="n">
-        <v>89</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -2655,19 +2659,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7181513409961686</v>
+        <v>0.7742656449553001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6819991000962641</v>
+        <v>0.7619805281240067</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8551921290850036</v>
+        <v>0.8640933658639238</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7899407729502577</v>
+        <v>0.7978455030996335</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7181513409961686</v>
+        <v>0.7742656449553001</v>
       </c>
     </row>
     <row r="3">
@@ -2677,19 +2681,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8996946206248532</v>
+        <v>0.9058805105316733</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8628615826475747</v>
+        <v>0.8793407831752361</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8158938175207181</v>
+        <v>0.8418356155955948</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8955316178181166</v>
+        <v>0.8961510532927121</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8996946206248532</v>
+        <v>0.9058805105316733</v>
       </c>
     </row>
     <row r="4">
@@ -2699,19 +2703,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9165136941038255</v>
+        <v>0.918936779499229</v>
       </c>
       <c r="C4" t="n">
-        <v>0.884806048017989</v>
+        <v>0.8918556334227971</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7145757379466262</v>
+        <v>0.7043655249366494</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8998699359891733</v>
+        <v>0.9037401733905115</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9165136941038255</v>
+        <v>0.918936779499229</v>
       </c>
     </row>
     <row r="5">
@@ -2721,19 +2725,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9071183859916254</v>
+        <v>0.9086410354015988</v>
       </c>
       <c r="C5" t="n">
-        <v>0.88227285252619</v>
+        <v>0.8854982213192496</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7998443713984255</v>
+        <v>0.7795843913411481</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9005407473376376</v>
+        <v>0.9017766023393871</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9071183859916254</v>
+        <v>0.9086410354015988</v>
       </c>
     </row>
     <row r="6">
@@ -2743,19 +2747,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9442326381101891</v>
+        <v>0.9455782312925171</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9259451593705914</v>
+        <v>0.9297368965707314</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7726891892142964</v>
+        <v>0.7605782182743097</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9393531989268127</v>
+        <v>0.9390968660571238</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9442326381101891</v>
+        <v>0.9455782312925171</v>
       </c>
     </row>
     <row r="7">
@@ -2765,19 +2769,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9548733433987586</v>
+        <v>0.9552088575742325</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9387413334079683</v>
+        <v>0.9397414688814231</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7342583783674149</v>
+        <v>0.7640442915195518</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9501867620789289</v>
+        <v>0.9499840166446412</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9548733433987586</v>
+        <v>0.9552088575742325</v>
       </c>
     </row>
     <row r="8">
@@ -2787,19 +2791,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.854860297808265</v>
+        <v>0.8560314539066421</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8107114745479892</v>
+        <v>0.8140841438583309</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8876883388855867</v>
+        <v>0.8857528914832316</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8621387447517662</v>
+        <v>0.8599125527343391</v>
       </c>
       <c r="F8" t="n">
-        <v>0.854860297808265</v>
+        <v>0.8560314539066421</v>
       </c>
     </row>
     <row r="9">
@@ -2809,19 +2813,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9435847208619002</v>
+        <v>0.9436500163238655</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9274613592877725</v>
+        <v>0.92985214748536</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7806410703897615</v>
+        <v>0.7919648139334003</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9341739878092744</v>
+        <v>0.9327057514908385</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9435847208619002</v>
+        <v>0.9436500163238655</v>
       </c>
     </row>
     <row r="10">
@@ -2831,19 +2835,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9307539023580206</v>
+        <v>0.9396379940219196</v>
       </c>
       <c r="C10" t="n">
-        <v>0.904654100540402</v>
+        <v>0.9256846196437281</v>
       </c>
       <c r="D10" t="n">
-        <v>0.855017866541093</v>
+        <v>0.8703236906333773</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9330298293746044</v>
+        <v>0.9336525734000952</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9307539023580206</v>
+        <v>0.9396379940219196</v>
       </c>
     </row>
     <row r="11">
@@ -2853,19 +2857,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8909561446457299</v>
+        <v>0.8959222214450584</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8489441643075906</v>
+        <v>0.8634012919620628</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7954712308326718</v>
+        <v>0.7989488410415807</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8596675078893556</v>
+        <v>0.8739632313834319</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8909561446457299</v>
+        <v>0.8959222214450584</v>
       </c>
     </row>
   </sheetData>
@@ -2911,16 +2915,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6880</v>
+        <v>7042</v>
       </c>
       <c r="C2" t="n">
-        <v>275</v>
+        <v>113</v>
       </c>
       <c r="D2" t="n">
-        <v>2827</v>
+        <v>3418</v>
       </c>
       <c r="E2" t="n">
-        <v>2546</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="3">
@@ -2930,16 +2934,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11322</v>
+        <v>11346</v>
       </c>
       <c r="C3" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>1178</v>
+        <v>1257</v>
       </c>
       <c r="E3" t="n">
-        <v>223</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4">
@@ -2949,16 +2953,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12372</v>
+        <v>12389</v>
       </c>
       <c r="C4" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="D4" t="n">
-        <v>1041</v>
+        <v>1098</v>
       </c>
       <c r="E4" t="n">
-        <v>150</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5">
@@ -2968,16 +2972,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11572</v>
+        <v>11588</v>
       </c>
       <c r="C5" t="n">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D5" t="n">
-        <v>1115</v>
+        <v>1153</v>
       </c>
       <c r="E5" t="n">
-        <v>365</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6">
@@ -2987,16 +2991,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12485</v>
+        <v>12493</v>
       </c>
       <c r="C6" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>706</v>
+        <v>722</v>
       </c>
       <c r="E6" t="n">
-        <v>154</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7">
@@ -3006,16 +3010,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11303</v>
+        <v>11307</v>
       </c>
       <c r="C7" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E7" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -3025,16 +3029,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9864</v>
+        <v>9874</v>
       </c>
       <c r="C8" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>1635</v>
+        <v>1699</v>
       </c>
       <c r="E8" t="n">
-        <v>409</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -3044,16 +3048,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14260</v>
+        <v>14263</v>
       </c>
       <c r="C9" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D9" t="n">
-        <v>778</v>
+        <v>802</v>
       </c>
       <c r="E9" t="n">
-        <v>212</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -3063,16 +3067,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11086</v>
+        <v>11104</v>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>756</v>
+        <v>830</v>
       </c>
       <c r="E10" t="n">
-        <v>180</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11">
@@ -3082,16 +3086,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12607</v>
+        <v>12649</v>
       </c>
       <c r="C11" t="n">
-        <v>106</v>
+        <v>64</v>
       </c>
       <c r="D11" t="n">
-        <v>1395</v>
+        <v>1495</v>
       </c>
       <c r="E11" t="n">
-        <v>189</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -3403,6 +3407,980 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>0.7181513409961686</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.6819991000962641</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.8551921290850036</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7899407729502577</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.7181513409961686</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ajeric_expert2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.8996946206248532</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.8628615826475747</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.8158938175207181</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8955316178181166</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8996946206248532</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ekamis_expert2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.9165136941038255</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.884806048017989</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7145757379466262</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8998699359891733</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9165136941038255</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>iguted_expert1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9071183859916254</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.88227285252619</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7998443713984255</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9005407473376376</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9071183859916254</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>inefoh_expert1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.9442326381101891</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9259451593705914</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.7726891892142964</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9393531989268127</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9442326381101891</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>otafeh_expert1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.9548733433987586</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9387413334079683</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7342583783674149</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9501867620789289</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9548733433987586</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>oxused_expert2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.854860297808265</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8107114745479892</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8876883388855867</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.8621387447517662</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.854860297808265</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pqbqpr_expert2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.9435847208619002</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9274613592877725</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7806410703897615</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9341739878092744</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9435847208619002</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>uhepah_expert1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.9307539023580206</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.904654100540402</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.855017866541093</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9330298293746044</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9307539023580206</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ukudab_expert2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.8909561446457299</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.8489441643075906</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.7954712308326718</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.8596675078893556</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.8909561446457299</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>true_negative</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>false_positive</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>false_negative</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>true_positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>afegip_expert1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>6624</v>
+      </c>
+      <c r="C2" t="n">
+        <v>531</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2209</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3164</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ajeric_expert2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>11295</v>
+      </c>
+      <c r="C3" t="n">
+        <v>75</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1082</v>
+      </c>
+      <c r="E3" t="n">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ekamis_expert2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>12361</v>
+      </c>
+      <c r="C4" t="n">
+        <v>67</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E4" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>iguted_expert1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>11564</v>
+      </c>
+      <c r="C5" t="n">
+        <v>91</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1034</v>
+      </c>
+      <c r="E5" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>inefoh_expert1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>12432</v>
+      </c>
+      <c r="C6" t="n">
+        <v>85</v>
+      </c>
+      <c r="D6" t="n">
+        <v>651</v>
+      </c>
+      <c r="E6" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>otafeh_expert1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>11290</v>
+      </c>
+      <c r="C7" t="n">
+        <v>31</v>
+      </c>
+      <c r="D7" t="n">
+        <v>493</v>
+      </c>
+      <c r="E7" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>oxused_expert2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>9840</v>
+      </c>
+      <c r="C8" t="n">
+        <v>70</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1507</v>
+      </c>
+      <c r="E8" t="n">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pqbqpr_expert2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>14131</v>
+      </c>
+      <c r="C9" t="n">
+        <v>194</v>
+      </c>
+      <c r="D9" t="n">
+        <v>727</v>
+      </c>
+      <c r="E9" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>uhepah_expert1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>11021</v>
+      </c>
+      <c r="C10" t="n">
+        <v>87</v>
+      </c>
+      <c r="D10" t="n">
+        <v>595</v>
+      </c>
+      <c r="E10" t="n">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ukudab_expert2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>12574</v>
+      </c>
+      <c r="C11" t="n">
+        <v>139</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1321</v>
+      </c>
+      <c r="E11" t="n">
+        <v>263</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>acc</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>roc_auc</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>prec</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>rec</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>afegip_expert1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.7812899106002554</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.7725313805905666</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.8490973905685479</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7955380694803192</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.7812899106002554</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ajeric_expert2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.9094041187064443</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.8859127231458003</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.83376844156423</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9012876312865306</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9094041187064443</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ekamis_expert2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.9205521697628314</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.8957505681481642</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.7713498432752672</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9066417202275033</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9205521697628314</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>iguted_expert1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9143509706889988</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8959944891110602</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7808520296358135</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9080774582077571</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9143509706889988</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>inefoh_expert1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.944980189878149</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9320956902863226</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8354361324412751</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9348526775909561</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.944980189878149</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>otafeh_expert1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.9560476430129173</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9427668276987762</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7584745619474418</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9490265123759837</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9560476430129173</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>oxused_expert2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.868077630918521</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8367817968371425</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8772895146336598</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.8701800196698085</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.868077630918521</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pqbqpr_expert2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.9398628795298727</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9293363502014738</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.8065604738484319</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9267918405713106</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9398628795298727</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>uhepah_expert1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.9433742942544006</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9334625647401761</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8730153577617118</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9369610862891609</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9433742942544006</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ukudab_expert2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.8978806742673288</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.8697599002455574</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.8095925728614708</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.8771540496166418</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.8978806742673288</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>true_negative</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>false_positive</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>false_negative</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>true_positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>afegip_expert1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>6880</v>
+      </c>
+      <c r="C2" t="n">
+        <v>275</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2827</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2546</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ajeric_expert2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>11322</v>
+      </c>
+      <c r="C3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1178</v>
+      </c>
+      <c r="E3" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ekamis_expert2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>12372</v>
+      </c>
+      <c r="C4" t="n">
+        <v>56</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1041</v>
+      </c>
+      <c r="E4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>iguted_expert1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>11572</v>
+      </c>
+      <c r="C5" t="n">
+        <v>83</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1115</v>
+      </c>
+      <c r="E5" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>inefoh_expert1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>12485</v>
+      </c>
+      <c r="C6" t="n">
+        <v>32</v>
+      </c>
+      <c r="D6" t="n">
+        <v>706</v>
+      </c>
+      <c r="E6" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>otafeh_expert1</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>11303</v>
+      </c>
+      <c r="C7" t="n">
+        <v>18</v>
+      </c>
+      <c r="D7" t="n">
+        <v>518</v>
+      </c>
+      <c r="E7" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>oxused_expert2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>9864</v>
+      </c>
+      <c r="C8" t="n">
+        <v>46</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1635</v>
+      </c>
+      <c r="E8" t="n">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pqbqpr_expert2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>14260</v>
+      </c>
+      <c r="C9" t="n">
+        <v>65</v>
+      </c>
+      <c r="D9" t="n">
+        <v>778</v>
+      </c>
+      <c r="E9" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>uhepah_expert1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>11086</v>
+      </c>
+      <c r="C10" t="n">
+        <v>22</v>
+      </c>
+      <c r="D10" t="n">
+        <v>756</v>
+      </c>
+      <c r="E10" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ukudab_expert2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>12607</v>
+      </c>
+      <c r="C11" t="n">
+        <v>106</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1395</v>
+      </c>
+      <c r="E11" t="n">
+        <v>189</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>acc</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>roc_auc</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>prec</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>rec</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>afegip_expert1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>0.7523946360153256</v>
       </c>
       <c r="C2" t="n">
